--- a/Antigravity/BD/Productos/TB_Productos.xlsx
+++ b/Antigravity/BD/Productos/TB_Productos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dashboard_Iconic\BD\Productos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dashboard_Iconic\Antigravity\BD\Productos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0748782B-D23D-4710-B651-F0FD06F93D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD9C2E0-F9E1-4A2C-9089-8D1E887604A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{210AB504-4FC3-4F33-895F-FB3205D1520F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="462">
   <si>
     <t>PD00001</t>
   </si>
@@ -1374,6 +1374,54 @@
   </si>
   <si>
     <t>MARCA_PRODUCTO</t>
+  </si>
+  <si>
+    <t>PD00198</t>
+  </si>
+  <si>
+    <t>ALTA YARI TORRONTES 2025</t>
+  </si>
+  <si>
+    <t>PD00199</t>
+  </si>
+  <si>
+    <t>ALTA YARI CHARDONNAY RESERVA 2025</t>
+  </si>
+  <si>
+    <t>PD00200</t>
+  </si>
+  <si>
+    <t>ALTA YARI CABERNET FRANC RESERVA 2024</t>
+  </si>
+  <si>
+    <t>PD00201</t>
+  </si>
+  <si>
+    <t>ALTA YARI PINOT NOIR 2024</t>
+  </si>
+  <si>
+    <t>PD00202</t>
+  </si>
+  <si>
+    <t>ALTA YARI GRAN TORRONTES 2025</t>
+  </si>
+  <si>
+    <t>PD00203</t>
+  </si>
+  <si>
+    <t>ALTA YARI GRAN MALBEC 2024</t>
+  </si>
+  <si>
+    <t>PD00204</t>
+  </si>
+  <si>
+    <t>ALTA YARI GRAN CORTE 2024</t>
+  </si>
+  <si>
+    <t>PD00205</t>
+  </si>
+  <si>
+    <t>ALTA YARI GRAN CALCAREO MALBEC 2024</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D98A35E-A040-45FE-9D0D-4DEC3FB32D2B}">
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="53.109375" bestFit="1" customWidth="1"/>
@@ -7076,6 +7124,214 @@
         <v>46078.541394942127</v>
       </c>
     </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H207" s="3">
+        <v>46154.800958599539</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H208" s="3">
+        <v>46154.803512037033</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H209" s="3">
+        <v>46154.806258796292</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H210" s="3">
+        <v>46154.809823958334</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H211" s="3">
+        <v>46154.812841817125</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H212" s="3">
+        <v>46154.81539895833</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H213" s="3">
+        <v>46154.816890972223</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H214" s="3">
+        <v>46154.81840575231</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
